--- a/event_registration_forms/022_professional_development_workshop_appointment_form--event_registration_forms.xlsx
+++ b/event_registration_forms/022_professional_development_workshop_appointment_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HH:MM (24h format)</t>
+          <t>HH -MM (24h format)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>workshop_time</t>
+          <t>workshop_time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Workshop Time</t>
+          <t>Workshop Time 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HH:MM (HH:MM format)</t>
+          <t>HH -MM (HH -MM format)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>participant_email</t>
+          <t>participant_email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Participant Email</t>
+          <t>Participant Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>participant_phone</t>
+          <t>participant_phone_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Participant Phone</t>
+          <t>Participant Phone 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>participant_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Participant Name</t>
+          <t>Participant Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
